--- a/exports/ICICIBANK_full_report.xlsx
+++ b/exports/ICICIBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:U74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.94</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.38541666666</v>
+        <v>44585.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>796.1</v>
+        <v>792</v>
       </c>
       <c r="I2" t="n">
         <v>795.3376804877464</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.18</v>
+        <v>-1.69</v>
       </c>
       <c r="L2" t="n">
-        <v>1.69</v>
+        <v>2.77</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.46</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>706.6</v>
+        <v>719.35</v>
       </c>
       <c r="I3" t="n">
         <v>707.8930009641734</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>10.78</v>
+        <v>9.17</v>
       </c>
       <c r="L3" t="n">
         <v>3.36</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.21</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44677.55208333334</v>
+        <v>44678.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>753.65</v>
+        <v>733.9</v>
       </c>
       <c r="I4" t="n">
         <v>735.1256257395419</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>4.77</v>
+        <v>2.02</v>
       </c>
       <c r="L4" t="n">
         <v>3.27</v>
@@ -669,7 +716,7 @@
         <v>1.98</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="O4" t="n">
         <v>1.88</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44707.38541666666</v>
+        <v>44707.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>724</v>
+        <v>732.2</v>
       </c>
       <c r="I5" t="n">
         <v>724.7303624448061</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>1.35</v>
+        <v>0.23</v>
       </c>
       <c r="L5" t="n">
         <v>3.55</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.32</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>732.25</v>
+        <v>722.7</v>
       </c>
       <c r="I6" t="n">
         <v>723.2054025677919</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01</v>
+        <v>-1.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -783,7 +854,7 @@
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="O6" t="n">
         <v>2.51</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>4.05</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>714.5</v>
+        <v>720.75</v>
       </c>
       <c r="I7" t="n">
         <v>715.237883066497</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>1.13</v>
+        <v>0.27</v>
       </c>
       <c r="L7" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="N7" t="n">
         <v>2.08</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.88</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>868</v>
+        <v>852.05</v>
       </c>
       <c r="I8" t="n">
         <v>854.822984978422</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>20.43</v>
+        <v>18.22</v>
       </c>
       <c r="L8" t="n">
         <v>3.7</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>4.6</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>873.35</v>
+        <v>889.25</v>
       </c>
       <c r="I9" t="n">
         <v>882.5525731150824</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.5</v>
+        <v>-4.37</v>
       </c>
       <c r="L9" t="n">
-        <v>3.44</v>
+        <v>4.54</v>
       </c>
       <c r="M9" t="n">
         <v>0.62</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>902.75</v>
+        <v>887.85</v>
       </c>
       <c r="I10" t="n">
         <v>893.2223228567784</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>1.52</v>
+        <v>-0.16</v>
       </c>
       <c r="L10" t="n">
         <v>2.95</v>
@@ -1011,7 +1130,7 @@
         <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
         <v>3.6</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.94</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>868</v>
+        <v>891.15</v>
       </c>
       <c r="I11" t="n">
         <v>887.640120792236</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>2.24</v>
+        <v>-0.37</v>
       </c>
       <c r="L11" t="n">
         <v>1.92</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.13</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44909.55208333334</v>
+        <v>44910.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>921</v>
+        <v>918.2</v>
       </c>
       <c r="I12" t="n">
         <v>919.342949428663</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="L12" t="n">
         <v>4.56</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>2.47</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>824.45</v>
+        <v>868.5</v>
       </c>
       <c r="I13" t="n">
         <v>854.6570735655525</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K13" t="n">
-        <v>10.21</v>
+        <v>5.41</v>
       </c>
       <c r="L13" t="n">
         <v>0.19</v>
       </c>
       <c r="M13" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>3.11</v>
       </c>
       <c r="O13" t="n">
         <v>-1.66</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.95</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44979.38541666666</v>
+        <v>44979.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>841.85</v>
+        <v>837.7</v>
       </c>
       <c r="I14" t="n">
         <v>841.0196955473916</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.07</v>
+        <v>-3.55</v>
       </c>
       <c r="L14" t="n">
         <v>5.22</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>3.89</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>851.1</v>
+        <v>867.4</v>
       </c>
       <c r="I15" t="n">
         <v>865.4685343132836</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6</v>
+        <v>-3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>3.14</v>
+        <v>4.14</v>
       </c>
       <c r="M15" t="n">
         <v>1.15</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.37</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>842.15</v>
+        <v>838.6</v>
       </c>
       <c r="I16" t="n">
         <v>840.3192924928107</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.91</v>
+        <v>-3.32</v>
       </c>
       <c r="L16" t="n">
         <v>3.59</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>4.83</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45007.55208333334</v>
+        <v>45008.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>858.15</v>
+        <v>865.3</v>
       </c>
       <c r="I17" t="n">
         <v>858.5536901310259</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.33</v>
+        <v>-3.18</v>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>3.37</v>
       </c>
       <c r="M17" t="n">
         <v>0.77</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.73</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45092.38541666666</v>
+        <v>45092.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>934.05</v>
+        <v>926.7</v>
       </c>
       <c r="I18" t="n">
         <v>928.4912564487718</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>84</v>
+        <v>84.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>7.95</v>
+        <v>7.1</v>
       </c>
       <c r="L18" t="n">
         <v>2.46</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>3.06</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45110.55208333334</v>
+        <v>45111.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>942.95</v>
+        <v>946.45</v>
       </c>
       <c r="I19" t="n">
         <v>944.1725910582238</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.75</v>
+        <v>-2.13</v>
       </c>
       <c r="L19" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="M19" t="n">
         <v>0.48</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>2.77</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45148.38541666666</v>
+        <v>45148.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>969.65</v>
+        <v>963.35</v>
       </c>
       <c r="I20" t="n">
         <v>965.5777159764899</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="L20" t="n">
         <v>0.58</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45180.38541666666</v>
+        <v>45180.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>971.5</v>
+        <v>982</v>
       </c>
       <c r="I21" t="n">
         <v>977.8619330152108</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.85</v>
+        <v>-1.94</v>
       </c>
       <c r="L21" t="n">
         <v>1.98</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>3.42</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45190.38541666666</v>
+        <v>45190.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>968</v>
+        <v>959.35</v>
       </c>
       <c r="I22" t="n">
         <v>965.746293126547</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.43</v>
+        <v>-2.31</v>
       </c>
       <c r="L22" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
         <v>0.8</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>3.88</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>933</v>
+        <v>943.15</v>
       </c>
       <c r="I23" t="n">
         <v>940.1650988712195</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>43</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>2.75</v>
+        <v>1.69</v>
       </c>
       <c r="L23" t="n">
         <v>1.04</v>
@@ -1752,7 +2027,7 @@
         <v>0.9</v>
       </c>
       <c r="N23" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="O23" t="n">
         <v>-2.85</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>3.33</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>927.45</v>
+        <v>917.35</v>
       </c>
       <c r="I24" t="n">
         <v>917.5115822219811</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.66</v>
+        <v>-2.74</v>
       </c>
       <c r="L24" t="n">
-        <v>2.72</v>
+        <v>3.01</v>
       </c>
       <c r="M24" t="n">
         <v>0.9</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>3.01</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45261.38541666666</v>
+        <v>45261.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>944.8</v>
+        <v>947.5</v>
       </c>
       <c r="I25" t="n">
         <v>944.9717187240342</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.99</v>
+        <v>-3.29</v>
       </c>
       <c r="L25" t="n">
-        <v>3.26</v>
+        <v>3.78</v>
       </c>
       <c r="M25" t="n">
         <v>0.1</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>2.59</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45282.38541666666</v>
+        <v>45282.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1000.5</v>
+        <v>994.75</v>
       </c>
       <c r="I26" t="n">
         <v>998.8824644264198</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="L26" t="n">
         <v>0.33</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>3.92</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1011.3</v>
+        <v>1034.9</v>
       </c>
       <c r="I27" t="n">
         <v>1012.681478117105</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.66</v>
+        <v>-4.04</v>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6</v>
+        <v>4.73</v>
       </c>
       <c r="N27" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="O27" t="n">
         <v>-1.02</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.1</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45330.38541666666</v>
+        <v>45330.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1001.9</v>
+        <v>991.9</v>
       </c>
       <c r="I28" t="n">
         <v>992.4533964065697</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.19</v>
+        <v>-4.15</v>
       </c>
       <c r="L28" t="n">
-        <v>4.52</v>
+        <v>4.8</v>
       </c>
       <c r="M28" t="n">
         <v>0.36</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.29</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45341.55208333334</v>
+        <v>45342.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1042</v>
+        <v>1048.4</v>
       </c>
       <c r="I29" t="n">
         <v>1043.877904803556</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.05</v>
+        <v>-5.7</v>
       </c>
       <c r="L29" t="n">
-        <v>5.45</v>
+        <v>6.12</v>
       </c>
       <c r="M29" t="n">
         <v>1.2</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.99</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1077.6</v>
+        <v>1065.6</v>
       </c>
       <c r="I30" t="n">
         <v>1072.909415435588</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>2.79</v>
+        <v>1.64</v>
       </c>
       <c r="L30" t="n">
         <v>1.45</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>3.96</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1096</v>
+        <v>1109.2</v>
       </c>
       <c r="I31" t="n">
         <v>1099.311938390115</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.85</v>
+        <v>-4.09</v>
       </c>
       <c r="L31" t="n">
-        <v>3.23</v>
+        <v>4.44</v>
       </c>
       <c r="M31" t="n">
         <v>1.15</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.17</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1119.85</v>
+        <v>1108.9</v>
       </c>
       <c r="I32" t="n">
         <v>1112.803303018656</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K32" t="n">
-        <v>0.96</v>
+        <v>-0.03</v>
       </c>
       <c r="L32" t="n">
         <v>1.74</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>4.52</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1121.85</v>
+        <v>1156</v>
       </c>
       <c r="I33" t="n">
         <v>1146.145698228389</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.17</v>
+        <v>-4.25</v>
       </c>
       <c r="L33" t="n">
-        <v>3.51</v>
+        <v>5.78</v>
       </c>
       <c r="M33" t="n">
-        <v>0.46</v>
+        <v>4.29</v>
       </c>
       <c r="N33" t="n">
-        <v>1.9</v>
+        <v>3.84</v>
       </c>
       <c r="O33" t="n">
         <v>-0.51</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>4.84</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1164.9</v>
+        <v>1084.05</v>
       </c>
       <c r="I34" t="n">
         <v>1100.063593653119</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.77</v>
+        <v>-6.22</v>
       </c>
       <c r="L34" t="n">
-        <v>1.7</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="O34" t="n">
         <v>3.84</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45464.55208333334</v>
+        <v>45467.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1157.4</v>
+        <v>1167.25</v>
       </c>
       <c r="I35" t="n">
         <v>1159.236928556087</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.77</v>
+        <v>-7.67</v>
       </c>
       <c r="L35" t="n">
-        <v>7.92</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>1.36</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>5.02</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1226.6</v>
+        <v>1199.9</v>
       </c>
       <c r="I36" t="n">
         <v>1206.983647102078</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K36" t="n">
-        <v>5.08</v>
+        <v>2.8</v>
       </c>
       <c r="L36" t="n">
         <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0.76</v>
+        <v>1.72</v>
       </c>
       <c r="N36" t="n">
-        <v>1.58</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
         <v>1.05</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.28</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45526.55208333334</v>
+        <v>45527.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1190.85</v>
+        <v>1203</v>
       </c>
       <c r="I37" t="n">
         <v>1202.679498451156</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K37" t="n">
-        <v>0.75</v>
+        <v>-0.26</v>
       </c>
       <c r="L37" t="n">
         <v>3.57</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>3.98</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1306.5</v>
+        <v>1276.25</v>
       </c>
       <c r="I38" t="n">
         <v>1277.340015461149</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K38" t="n">
-        <v>8.6</v>
+        <v>6.09</v>
       </c>
       <c r="L38" t="n">
         <v>1.2</v>
@@ -2607,7 +3062,7 @@
         <v>1.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="O38" t="n">
         <v>1.15</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45590.55208333334</v>
+        <v>45593.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1259.6</v>
+        <v>1304.95</v>
       </c>
       <c r="I39" t="n">
         <v>1275.385619478303</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>1.3</v>
+        <v>-2.25</v>
       </c>
       <c r="L39" t="n">
-        <v>1.61</v>
+        <v>2.47</v>
       </c>
       <c r="M39" t="n">
-        <v>0.72</v>
+        <v>2.06</v>
       </c>
       <c r="N39" t="n">
         <v>2.86</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.86</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45609.38541666666</v>
+        <v>45609.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1265.95</v>
+        <v>1258</v>
       </c>
       <c r="I40" t="n">
         <v>1258.266731281557</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.99</v>
+        <v>-3.6</v>
       </c>
       <c r="L40" t="n">
         <v>4.47</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.67</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1278</v>
+        <v>1301</v>
       </c>
       <c r="I41" t="n">
         <v>1294.150272108608</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.59</v>
+        <v>-3.42</v>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>4.23</v>
       </c>
       <c r="M41" t="n">
-        <v>0.38</v>
+        <v>1.41</v>
       </c>
       <c r="N41" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="O41" t="n">
         <v>-0.87</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.13</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1316.9</v>
+        <v>1289.5</v>
       </c>
       <c r="I42" t="n">
         <v>1308.779746998425</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>1.22</v>
+        <v>-0.88</v>
       </c>
       <c r="L42" t="n">
         <v>1.44</v>
       </c>
       <c r="M42" t="n">
-        <v>0.66</v>
+        <v>2.35</v>
       </c>
       <c r="N42" t="n">
-        <v>1.28</v>
+        <v>2.08</v>
       </c>
       <c r="O42" t="n">
         <v>1.96</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>4</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45684.55208333334</v>
+        <v>45685.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1225.25</v>
+        <v>1256.75</v>
       </c>
       <c r="I43" t="n">
         <v>1247.727116641272</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K43" t="n">
-        <v>4.98</v>
+        <v>2.54</v>
       </c>
       <c r="L43" t="n">
         <v>2.87</v>
       </c>
       <c r="M43" t="n">
-        <v>0.64</v>
+        <v>1.8</v>
       </c>
       <c r="N43" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="O43" t="n">
         <v>-2.08</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>5.16</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45709.55208333334</v>
+        <v>45712.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1232</v>
+        <v>1217.75</v>
       </c>
       <c r="I44" t="n">
         <v>1224.530146210189</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.97</v>
+        <v>-3.1</v>
       </c>
       <c r="L44" t="n">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="M44" t="n">
         <v>0.62</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>4.1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45728.55208333334</v>
+        <v>45729.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1244.45</v>
+        <v>1252</v>
       </c>
       <c r="I45" t="n">
         <v>1248.370111664195</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.19</v>
+        <v>-2.81</v>
       </c>
       <c r="L45" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="M45" t="n">
         <v>1.07</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>3.29</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1335.05</v>
+        <v>1270.25</v>
       </c>
       <c r="I46" t="n">
         <v>1310.573179636831</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K46" t="n">
-        <v>6.63</v>
+        <v>1.46</v>
       </c>
       <c r="L46" t="n">
         <v>0.54</v>
       </c>
       <c r="M46" t="n">
-        <v>0.59</v>
+        <v>2.98</v>
       </c>
       <c r="N46" t="n">
-        <v>2.21</v>
+        <v>3.07</v>
       </c>
       <c r="O46" t="n">
         <v>0.34</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>6.83</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1312.05</v>
+        <v>1345.9</v>
       </c>
       <c r="I47" t="n">
         <v>1344.530309009303</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.29</v>
+        <v>-5.96</v>
       </c>
       <c r="L47" t="n">
-        <v>4.31</v>
+        <v>6.36</v>
       </c>
       <c r="M47" t="n">
-        <v>0.44</v>
+        <v>2.97</v>
       </c>
       <c r="N47" t="n">
-        <v>0.62</v>
+        <v>2.9</v>
       </c>
       <c r="O47" t="n">
         <v>-3.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45786.38541666666</v>
+        <v>45786.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1393.5</v>
+        <v>1389</v>
       </c>
       <c r="I48" t="n">
         <v>1393.115344842605</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="L48" t="n">
         <v>0.72</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>3.89</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1440.1</v>
+        <v>1451.7</v>
       </c>
       <c r="I49" t="n">
         <v>1443.032413609741</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.68</v>
+        <v>-4.51</v>
       </c>
       <c r="L49" t="n">
-        <v>3.74</v>
+        <v>4.61</v>
       </c>
       <c r="M49" t="n">
         <v>1.47</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>4.55</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1424.5</v>
+        <v>1415</v>
       </c>
       <c r="I50" t="n">
         <v>1419.472494466283</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.87</v>
+        <v>-2.53</v>
       </c>
       <c r="L50" t="n">
-        <v>2.49</v>
+        <v>3.31</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8</v>
+        <v>1.47</v>
       </c>
       <c r="N50" t="n">
         <v>1.75</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>2.68</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1440</v>
+        <v>1453</v>
       </c>
       <c r="I51" t="n">
         <v>1445.260140546808</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.77</v>
+        <v>-2.69</v>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="M51" t="n">
         <v>0.61</v>
       </c>
       <c r="N51" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="O51" t="n">
         <v>-0.48</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>3.26</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1418.4</v>
+        <v>1414.6</v>
       </c>
       <c r="I52" t="n">
         <v>1418.081473486553</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.38</v>
+        <v>-2.64</v>
       </c>
       <c r="L52" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="M52" t="n">
         <v>0.49</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>2.27</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1426.7</v>
+        <v>1460.5</v>
       </c>
       <c r="I53" t="n">
         <v>1446.747982366248</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.86</v>
+        <v>-3.24</v>
       </c>
       <c r="L53" t="n">
-        <v>1.02</v>
+        <v>3.63</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="N53" t="n">
-        <v>0.59</v>
+        <v>2.65</v>
       </c>
       <c r="O53" t="n">
         <v>0.59</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>3.43</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1463.1</v>
+        <v>1443.6</v>
       </c>
       <c r="I54" t="n">
         <v>1449.843665242369</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
-        <v>0.18</v>
+        <v>-1.16</v>
       </c>
       <c r="L54" t="n">
         <v>1.61</v>
@@ -3519,7 +4166,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>0.97</v>
+        <v>1.24</v>
       </c>
       <c r="O54" t="n">
         <v>2.65</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>3.36</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1417.5</v>
+        <v>1423.2</v>
       </c>
       <c r="I55" t="n">
         <v>1422.558220842245</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="L55" t="n">
         <v>1.24</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>2.31</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45923.38541666666</v>
+        <v>45923.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1399.3</v>
+        <v>1396.1</v>
       </c>
       <c r="I56" t="n">
         <v>1396.143665600883</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.68</v>
+        <v>-1.9</v>
       </c>
       <c r="L56" t="n">
         <v>2.26</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>2.27</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1384.8</v>
+        <v>1396.1</v>
       </c>
       <c r="I57" t="n">
         <v>1386.629612467471</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0.3</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>2.78</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45950.55208333334</v>
+        <v>45951.57291666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1393</v>
+        <v>1381.3</v>
       </c>
       <c r="I58" t="n">
         <v>1392.31732036566</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6.1875</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.22</v>
+        <v>-1.06</v>
       </c>
       <c r="L58" t="n">
-        <v>0.76</v>
+        <v>1.45</v>
       </c>
       <c r="M58" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="N58" t="n">
         <v>3.07</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>3.47</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1359</v>
+        <v>1365.4</v>
       </c>
       <c r="I59" t="n">
         <v>1359.531667997132</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20.97916666666667</v>
+        <v>21.8125</v>
       </c>
       <c r="K59" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="L59" t="n">
         <v>0.62</v>
       </c>
       <c r="M59" t="n">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N59" t="n">
         <v>1.69</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>2.5</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46001.55208333334</v>
+        <v>46002.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1364.5</v>
+        <v>1359</v>
       </c>
       <c r="I60" t="n">
         <v>1359.879428269167</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.47</v>
       </c>
       <c r="L60" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="M60" t="n">
         <v>0.82</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>2.47</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46024.55208333334</v>
+        <v>46027.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1355.8</v>
+        <v>1371.8</v>
       </c>
       <c r="I61" t="n">
         <v>1365.102517769789</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>0.24</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>0.91</v>
+        <v>1.21</v>
       </c>
       <c r="M61" t="n">
         <v>0.51</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>2.88</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1413.9</v>
+        <v>1369.6</v>
       </c>
       <c r="I62" t="n">
         <v>1394.832477368427</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>3.07</v>
+        <v>-0.16</v>
       </c>
       <c r="L62" t="n">
         <v>1.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="N62" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="O62" t="n">
         <v>1.19</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.57</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1388</v>
+        <v>1407.5</v>
       </c>
       <c r="I63" t="n">
         <v>1397.785050781298</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.34</v>
+        <v>-2.77</v>
       </c>
       <c r="L63" t="n">
         <v>3.46</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.39</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46080.38541666666</v>
+        <v>46080.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1383.7</v>
+        <v>1379.4</v>
       </c>
       <c r="I64" t="n">
         <v>1383.183619877364</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.69</v>
+        <v>-2</v>
       </c>
       <c r="L64" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="M64" t="n">
         <v>0.8100000000000001</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>3.32</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1248</v>
+        <v>1310.7</v>
       </c>
       <c r="I65" t="n">
         <v>1258.79845970321</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>9.529999999999999</v>
+        <v>4.98</v>
       </c>
       <c r="L65" t="n">
         <v>0.78</v>
       </c>
       <c r="M65" t="n">
-        <v>1.35</v>
+        <v>4.97</v>
       </c>
       <c r="N65" t="n">
-        <v>2.96</v>
+        <v>4.89</v>
       </c>
       <c r="O65" t="n">
         <v>-1.58</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.06</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46136.38541666666</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1331</v>
+        <v>1325.7</v>
       </c>
       <c r="I66" t="n">
         <v>1327.054237697045</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="L66" t="n">
         <v>2.66</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.07</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1267.2</v>
+        <v>1281.3</v>
       </c>
       <c r="I67" t="n">
         <v>1278.140659651039</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>4.41</v>
+        <v>3.35</v>
       </c>
       <c r="L67" t="n">
         <v>0.77</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.01</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1259</v>
+        <v>1241.9</v>
       </c>
       <c r="I68" t="n">
         <v>1244.593820748958</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.74</v>
+        <v>-3.08</v>
       </c>
       <c r="L68" t="n">
-        <v>2.61</v>
+        <v>3.11</v>
       </c>
       <c r="M68" t="n">
         <v>0.27</v>
       </c>
       <c r="N68" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="O68" t="n">
         <v>2.08</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>4.98</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1273.8</v>
+        <v>1298.9</v>
       </c>
       <c r="I69" t="n">
         <v>1275.560128306789</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.57</v>
+        <v>-4.59</v>
       </c>
       <c r="L69" t="n">
-        <v>3.06</v>
+        <v>5.16</v>
       </c>
       <c r="M69" t="n">
         <v>0.41</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.85</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46246.55208333334</v>
+        <v>46247.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1426.1</v>
+        <v>1409.5</v>
       </c>
       <c r="I70" t="n">
         <v>1409.779286695435</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K70" t="n">
-        <v>9.789999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="L70" t="n">
         <v>2.12</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>4.03</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1434.4</v>
+        <v>1449.8</v>
       </c>
       <c r="I71" t="n">
         <v>1439.970000638646</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.77</v>
+        <v>-2.86</v>
       </c>
       <c r="L71" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="M71" t="n">
         <v>0.82</v>
       </c>
       <c r="N71" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="O71" t="n">
         <v>-1.07</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>3.17</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46272.55208333334</v>
+        <v>46273.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1423.6</v>
+        <v>1398.2</v>
       </c>
       <c r="I72" t="n">
         <v>1409.533510789029</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.81</v>
+        <v>-3.56</v>
       </c>
       <c r="L72" t="n">
-        <v>2.13</v>
+        <v>3.69</v>
       </c>
       <c r="M72" t="n">
         <v>0.84</v>
       </c>
       <c r="N72" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="O72" t="n">
         <v>0.89</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.09</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1333.2</v>
+        <v>1340.2</v>
       </c>
       <c r="I73" t="n">
         <v>1335.220725277279</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K73" t="n">
-        <v>4.65</v>
+        <v>4.15</v>
       </c>
       <c r="L73" t="n">
         <v>1.91</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4662,6 +5549,14 @@
       <c r="Q74" t="n">
         <v>32</v>
       </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6764,7 +7659,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -6774,7 +7669,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6784,7 +7679,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="8">
@@ -6794,7 +7689,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6804,7 +7699,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="10">
@@ -6814,7 +7709,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.7</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="11">
@@ -6824,7 +7719,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -6834,7 +7729,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -6844,7 +7739,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6854,7 +7749,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.98</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="15">
@@ -6864,7 +7759,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.68</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="16">
@@ -6874,7 +7769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.28</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="17">
@@ -6884,7 +7779,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.43</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="18">
@@ -6894,7 +7789,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6904,7 +7799,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="20">
@@ -6914,7 +7809,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.12</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="21">
@@ -6924,7 +7819,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.92</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -6934,7 +7829,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -6954,7 +7849,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.99</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="25">
@@ -6964,7 +7859,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.52</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="26">
@@ -6974,7 +7869,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="27">
@@ -6984,7 +7879,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="28">
@@ -6994,7 +7889,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
